--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mazenelnahla/Desktop/Projects/University Schedule System/degree/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mazenelnahla/Desktop/Projects/React Projects/degree/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1A2133-5737-7343-932C-1BD3B77DB81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4457450D-E00B-204B-9A39-00B356085183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3180" yWindow="2080" windowWidth="27640" windowHeight="16680" xr2:uid="{685E02A3-3CA7-7740-8516-46D23A04F233}"/>
   </bookViews>
@@ -837,6 +837,162 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -846,15 +1002,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -865,154 +1012,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1522,13 +1522,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>9575</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
+      <xdr:rowOff>70089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>182880</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>225423</xdr:rowOff>
+      <xdr:rowOff>70089</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1543,8 +1543,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11023315520" y="11282680"/>
-          <a:ext cx="846405" cy="4443"/>
+          <a:off x="13522462764" y="7929000"/>
+          <a:ext cx="999015" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1617,13 +1617,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>469900</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>226060</xdr:rowOff>
+      <xdr:rowOff>148783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>210026</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>226060</xdr:rowOff>
+      <xdr:rowOff>148783</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1638,8 +1638,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="11021269074" y="11287760"/>
-          <a:ext cx="1086326" cy="0"/>
+          <a:off x="13510652686" y="7962512"/>
+          <a:ext cx="1390408" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1710,15 +1710,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:colOff>557023</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>161973</xdr:rowOff>
+      <xdr:rowOff>166165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>317184</xdr:colOff>
+      <xdr:colOff>325567</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:rowOff>179452</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1733,8 +1733,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022508116" y="11223673"/>
-          <a:ext cx="3807144" cy="13287"/>
+          <a:off x="13521494367" y="8025076"/>
+          <a:ext cx="4722802" cy="13287"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1858,9 +1858,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>191508</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:rowOff>63836</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1875,8 +1875,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11023307900" y="9710700"/>
-          <a:ext cx="22659" cy="4139920"/>
+          <a:off x="13535528968" y="6892913"/>
+          <a:ext cx="23667" cy="2857193"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2245,9 +2245,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>228249</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
+      <xdr:rowOff>111198</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2262,8 +2262,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11023269800" y="7281114"/>
-          <a:ext cx="4651" cy="1372666"/>
+          <a:off x="13514192903" y="5190355"/>
+          <a:ext cx="4300" cy="937249"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2286,15 +2286,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>497019</xdr:colOff>
+      <xdr:colOff>462350</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>205367</xdr:rowOff>
+      <xdr:rowOff>70230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>239246</xdr:colOff>
+      <xdr:colOff>239954</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>205367</xdr:rowOff>
+      <xdr:rowOff>99493</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2309,8 +2309,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="11023259154" y="8638167"/>
-          <a:ext cx="3107727" cy="0"/>
+          <a:off x="13514181198" y="6086636"/>
+          <a:ext cx="3903641" cy="29263"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2668,7 +2668,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
+      <xdr:colOff>207412</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>42532</xdr:rowOff>
     </xdr:from>
@@ -2676,7 +2676,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>218036</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>236220</xdr:rowOff>
+      <xdr:rowOff>153166</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2691,8 +2691,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11021261064" y="9935832"/>
-          <a:ext cx="4676" cy="1362088"/>
+          <a:off x="13532193572" y="7100924"/>
+          <a:ext cx="10624" cy="953046"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3004,13 +3004,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>56768</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>2155</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>215917</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3025,8 +3025,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11024163880" y="9954260"/>
-          <a:ext cx="0" cy="233295"/>
+          <a:off x="13523463734" y="7077395"/>
+          <a:ext cx="0" cy="159149"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3289,13 +3289,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>5894</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>157480</xdr:rowOff>
+      <xdr:rowOff>60474</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>188148</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:rowOff>60750</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3309,9 +3309,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11023307900" y="13848080"/>
-          <a:ext cx="857706" cy="10160"/>
+        <a:xfrm>
+          <a:off x="13535532328" y="9746744"/>
+          <a:ext cx="1008762" cy="276"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3645,6 +3645,150 @@
         <a:xfrm flipH="1">
           <a:off x="11026333813" y="5925379"/>
           <a:ext cx="0" cy="171010"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>12575</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>67062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>12575</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>8257</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="رابط كسهم مستقيم 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2669D9B0-5C2F-D444-81C4-D30700F5E041}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="13523458779" y="7925973"/>
+          <a:ext cx="0" cy="159149"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6231</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>56845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6231</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>213066</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="رابط كسهم مستقيم 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A3BFC05-B954-E64F-AAF2-AAE882336FF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="13536540753" y="9743115"/>
+          <a:ext cx="0" cy="156221"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>450645</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>58526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>450645</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>11427</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="64" name="رابط كسهم مستقيم 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F334BD89-7089-D34C-972C-E7EDFF9BDA03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="13518096544" y="6074932"/>
+          <a:ext cx="0" cy="157739"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3989,96 +4133,96 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:24" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="12"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="64"/>
     </row>
     <row r="2" spans="1:24" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16" t="s">
+      <c r="D2" s="55"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="19" t="s">
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="21" t="s">
+      <c r="N2" s="48"/>
+      <c r="O2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="P2" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="21"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
     </row>
     <row r="3" spans="1:24" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="55"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="19" t="s">
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="20"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="21"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="49"/>
     </row>
     <row r="4" spans="1:24" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="25"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="52"/>
     </row>
     <row r="6" spans="1:24" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4111,10 +4255,10 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
@@ -4159,69 +4303,69 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="46"/>
+      <c r="W7" s="21"/>
       <c r="X7" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="28" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="29"/>
+      <c r="D8" s="45"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="33"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="33"/>
+      <c r="M8" s="39"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="36" t="s">
+      <c r="O8" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="P8" s="37"/>
+      <c r="P8" s="59"/>
       <c r="Q8" s="1"/>
-      <c r="R8" s="40" t="s">
+      <c r="R8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="S8" s="41"/>
+      <c r="S8" s="28"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="47"/>
+      <c r="W8" s="22"/>
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="35"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="39"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="61"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="43"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -4229,8 +4373,8 @@
       <c r="X9" s="1"/>
     </row>
     <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -4240,8 +4384,8 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="43"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -4255,8 +4399,8 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
@@ -4301,69 +4445,69 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
-      <c r="W11" s="46"/>
+      <c r="W11" s="21"/>
       <c r="X11" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="28" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="39"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="33"/>
+      <c r="J12" s="39"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="33"/>
+      <c r="M12" s="39"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="32" t="s">
+      <c r="O12" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="33"/>
+      <c r="P12" s="39"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="40" t="s">
+      <c r="R12" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="S12" s="41"/>
+      <c r="S12" s="28"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
-      <c r="W12" s="47"/>
+      <c r="W12" s="22"/>
       <c r="X12" s="1"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="41"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="35"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="41"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="43"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="30"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -4382,8 +4526,8 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="36"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
@@ -4408,8 +4552,8 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -4423,7 +4567,7 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="1"/>
@@ -4471,69 +4615,69 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
-      <c r="W16" s="46"/>
+      <c r="W16" s="21"/>
       <c r="X16" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="52"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="52"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="52"/>
+      <c r="J17" s="17"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="51" t="s">
+      <c r="L17" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="M17" s="52"/>
+      <c r="M17" s="17"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="55" t="s">
+      <c r="O17" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="P17" s="56"/>
+      <c r="P17" s="32"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="40" t="s">
+      <c r="R17" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="S17" s="41"/>
+      <c r="S17" s="28"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
-      <c r="W17" s="47"/>
+      <c r="W17" s="22"/>
       <c r="X17" s="1"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="54"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="54"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="54"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="54"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="19"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="58"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="34"/>
       <c r="Q18" s="1"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="43"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="30"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -4541,7 +4685,7 @@
       <c r="X18" s="1"/>
     </row>
     <row r="19" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -4567,7 +4711,7 @@
       <c r="X19" s="1"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="1"/>
       <c r="C20" s="5" t="s">
         <v>50</v>
@@ -4613,69 +4757,69 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="46"/>
+      <c r="W20" s="21"/>
       <c r="X20" s="8">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="33"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="52"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="52"/>
+      <c r="J21" s="17"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="51" t="s">
+      <c r="L21" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M21" s="52"/>
+      <c r="M21" s="17"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="51" t="s">
+      <c r="O21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="P21" s="52"/>
+      <c r="P21" s="17"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="40" t="s">
+      <c r="R21" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="S21" s="41"/>
+      <c r="S21" s="28"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="47"/>
+      <c r="W21" s="22"/>
       <c r="X21" s="1"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="54"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="54"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="54"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="19"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="54"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="19"/>
       <c r="Q22" s="1"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="43"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="30"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -4735,7 +4879,7 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="20" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="1"/>
@@ -4787,79 +4931,79 @@
       <c r="V25" s="5">
         <v>1</v>
       </c>
-      <c r="W25" s="46"/>
+      <c r="W25" s="21"/>
       <c r="X25" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="52"/>
+      <c r="D26" s="17"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G26" s="52"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="59" t="s">
+      <c r="I26" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="60"/>
+      <c r="J26" s="24"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="51" t="s">
+      <c r="L26" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="M26" s="52"/>
+      <c r="M26" s="17"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="40" t="s">
+      <c r="O26" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="P26" s="41"/>
+      <c r="P26" s="28"/>
       <c r="Q26" s="1"/>
-      <c r="R26" s="40" t="s">
+      <c r="R26" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="S26" s="41"/>
+      <c r="S26" s="28"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="55" t="s">
+      <c r="U26" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="V26" s="56"/>
-      <c r="W26" s="47"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="22"/>
       <c r="X26" s="1"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="26"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="54"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="19"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="62"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="26"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="54"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="19"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="43"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="30"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="43"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="30"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="58"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="34"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -4884,7 +5028,7 @@
       <c r="X28" s="1"/>
     </row>
     <row r="29" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="1"/>
       <c r="C29" s="5" t="s">
         <v>77</v>
@@ -4934,69 +5078,69 @@
       <c r="X29" s="1"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="17"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G30" s="52"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="59" t="s">
+      <c r="I30" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="J30" s="60"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="51" t="s">
+      <c r="L30" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="M30" s="52"/>
+      <c r="M30" s="17"/>
       <c r="N30" s="1"/>
-      <c r="O30" s="51" t="s">
+      <c r="O30" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="P30" s="52"/>
+      <c r="P30" s="17"/>
       <c r="Q30" s="1"/>
-      <c r="R30" s="40" t="s">
+      <c r="R30" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="S30" s="41"/>
+      <c r="S30" s="28"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
-      <c r="W30" s="46"/>
+      <c r="W30" s="21"/>
       <c r="X30" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="54"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="54"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="62"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="26"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="54"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="19"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="54"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="19"/>
       <c r="Q31" s="1"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="43"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="30"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
-      <c r="W31" s="47"/>
+      <c r="W31" s="22"/>
       <c r="X31" s="1"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
@@ -5052,7 +5196,7 @@
       <c r="X33" s="1"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B34" s="1"/>
@@ -5104,79 +5248,79 @@
       <c r="V34" s="5">
         <v>1</v>
       </c>
-      <c r="W34" s="46"/>
+      <c r="W34" s="21"/>
       <c r="X34" s="7">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="52"/>
+      <c r="D35" s="17"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="59" t="s">
+      <c r="F35" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G35" s="60"/>
+      <c r="G35" s="24"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="J35" s="52"/>
+      <c r="J35" s="17"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="59" t="s">
+      <c r="L35" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="M35" s="60"/>
+      <c r="M35" s="24"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="51" t="s">
+      <c r="O35" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="P35" s="52"/>
+      <c r="P35" s="17"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="55" t="s">
+      <c r="R35" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="S35" s="56"/>
+      <c r="S35" s="32"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="55" t="s">
+      <c r="U35" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="V35" s="56"/>
-      <c r="W35" s="47"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="22"/>
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A36" s="26"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="54"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="62"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="54"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="19"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="62"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="26"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="54"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="19"/>
       <c r="Q36" s="1"/>
-      <c r="R36" s="57"/>
-      <c r="S36" s="58"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="34"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="57"/>
-      <c r="V36" s="58"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="34"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
     </row>
     <row r="37" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -5202,7 +5346,7 @@
       <c r="X37" s="1"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A38" s="26"/>
+      <c r="A38" s="20"/>
       <c r="B38" s="1"/>
       <c r="C38" s="5" t="s">
         <v>104</v>
@@ -5248,69 +5392,69 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="46"/>
+      <c r="W38" s="21"/>
       <c r="X38" s="7">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="60"/>
+      <c r="D39" s="24"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="59" t="s">
+      <c r="F39" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G39" s="60"/>
+      <c r="G39" s="24"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="51" t="s">
+      <c r="I39" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="J39" s="52"/>
+      <c r="J39" s="17"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="59" t="s">
+      <c r="L39" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="60"/>
+      <c r="M39" s="24"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="51" t="s">
+      <c r="O39" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="P39" s="52"/>
+      <c r="P39" s="17"/>
       <c r="Q39" s="1"/>
-      <c r="R39" s="55" t="s">
+      <c r="R39" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="S39" s="56"/>
+      <c r="S39" s="32"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="47"/>
+      <c r="W39" s="22"/>
       <c r="X39" s="1"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A40" s="26"/>
+      <c r="A40" s="20"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="62"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="54"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="19"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="62"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="26"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="54"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="19"/>
       <c r="Q40" s="1"/>
-      <c r="R40" s="57"/>
-      <c r="S40" s="58"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="34"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
@@ -5370,7 +5514,7 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="20" t="s">
         <v>116</v>
       </c>
       <c r="B43" s="1"/>
@@ -5414,64 +5558,64 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
-      <c r="W43" s="46"/>
+      <c r="W43" s="21"/>
       <c r="X43" s="7">
         <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
+      <c r="A44" s="20"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="59" t="s">
+      <c r="C44" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="60"/>
+      <c r="D44" s="24"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="60"/>
+      <c r="G44" s="24"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="59" t="s">
+      <c r="I44" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J44" s="60"/>
+      <c r="J44" s="24"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="59" t="s">
+      <c r="L44" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="M44" s="60"/>
+      <c r="M44" s="24"/>
       <c r="N44" s="1"/>
-      <c r="O44" s="59" t="s">
+      <c r="O44" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="P44" s="60"/>
+      <c r="P44" s="24"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
-      <c r="W44" s="47"/>
+      <c r="W44" s="22"/>
       <c r="X44" s="1"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A45" s="26"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="62"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="26"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="62"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="61"/>
-      <c r="J45" s="62"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="26"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="61"/>
-      <c r="M45" s="62"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="26"/>
       <c r="N45" s="1"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="62"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="26"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -5482,7 +5626,7 @@
       <c r="X45" s="1"/>
     </row>
     <row r="46" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="26"/>
+      <c r="A46" s="20"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -5508,7 +5652,7 @@
       <c r="X46" s="1"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A47" s="26"/>
+      <c r="A47" s="20"/>
       <c r="B47" s="1"/>
       <c r="C47" s="5" t="s">
         <v>126</v>
@@ -5550,64 +5694,64 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="46"/>
+      <c r="W47" s="21"/>
       <c r="X47" s="7">
         <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="52"/>
+      <c r="D48" s="17"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="59" t="s">
+      <c r="F48" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="G48" s="60"/>
+      <c r="G48" s="24"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="59" t="s">
+      <c r="I48" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="60"/>
+      <c r="J48" s="24"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="59" t="s">
+      <c r="L48" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="M48" s="60"/>
+      <c r="M48" s="24"/>
       <c r="N48" s="1"/>
-      <c r="O48" s="59" t="s">
+      <c r="O48" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="P48" s="60"/>
+      <c r="P48" s="24"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="47"/>
+      <c r="W48" s="22"/>
       <c r="X48" s="1"/>
     </row>
     <row r="49" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="54"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="62"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="26"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="62"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="26"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="62"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="26"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="62"/>
+      <c r="O49" s="25"/>
+      <c r="P49" s="26"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -5618,21 +5762,98 @@
       <c r="X49" s="1"/>
     </row>
     <row r="50" spans="1:24" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="W50" s="63" t="s">
+      <c r="W50" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="X50" s="64"/>
+      <c r="X50" s="11"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="W51" s="65"/>
-      <c r="X51" s="66"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="13"/>
     </row>
     <row r="52" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="W52" s="67"/>
-      <c r="X52" s="68"/>
+      <c r="W52" s="14"/>
+      <c r="X52" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="93">
+    <mergeCell ref="D1:Q1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="I8:J9"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="O8:P9"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="L12:M13"/>
+    <mergeCell ref="O12:P13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="R21:S22"/>
+    <mergeCell ref="L14:M15"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="F17:G18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="O17:P18"/>
+    <mergeCell ref="R17:S18"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="F21:G22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="L21:M22"/>
+    <mergeCell ref="O21:P22"/>
+    <mergeCell ref="W30:W31"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="F26:G27"/>
+    <mergeCell ref="I26:J27"/>
+    <mergeCell ref="L26:M27"/>
+    <mergeCell ref="O26:P27"/>
+    <mergeCell ref="R26:S27"/>
+    <mergeCell ref="U26:V27"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="F30:G31"/>
+    <mergeCell ref="I30:J31"/>
+    <mergeCell ref="L30:M31"/>
+    <mergeCell ref="O30:P31"/>
+    <mergeCell ref="R30:S31"/>
+    <mergeCell ref="R39:S40"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="W34:W35"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="L35:M36"/>
+    <mergeCell ref="O35:P36"/>
+    <mergeCell ref="R35:S36"/>
+    <mergeCell ref="U35:V36"/>
+    <mergeCell ref="W38:W39"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="F39:G40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="L39:M40"/>
     <mergeCell ref="W50:X50"/>
     <mergeCell ref="W51:X52"/>
     <mergeCell ref="O39:P40"/>
@@ -5649,83 +5870,6 @@
     <mergeCell ref="I48:J49"/>
     <mergeCell ref="L48:M49"/>
     <mergeCell ref="O48:P49"/>
-    <mergeCell ref="R30:S31"/>
-    <mergeCell ref="R39:S40"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="W34:W35"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="L35:M36"/>
-    <mergeCell ref="O35:P36"/>
-    <mergeCell ref="R35:S36"/>
-    <mergeCell ref="U35:V36"/>
-    <mergeCell ref="W38:W39"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="F39:G40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="L39:M40"/>
-    <mergeCell ref="O21:P22"/>
-    <mergeCell ref="W30:W31"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="W25:W26"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="F26:G27"/>
-    <mergeCell ref="I26:J27"/>
-    <mergeCell ref="L26:M27"/>
-    <mergeCell ref="O26:P27"/>
-    <mergeCell ref="R26:S27"/>
-    <mergeCell ref="U26:V27"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="F30:G31"/>
-    <mergeCell ref="I30:J31"/>
-    <mergeCell ref="L30:M31"/>
-    <mergeCell ref="O30:P31"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="R21:S22"/>
-    <mergeCell ref="L14:M15"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="F17:G18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="L17:M18"/>
-    <mergeCell ref="O17:P18"/>
-    <mergeCell ref="R17:S18"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="F21:G22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="L21:M22"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="L12:M13"/>
-    <mergeCell ref="O12:P13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="I8:J9"/>
-    <mergeCell ref="L8:M9"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="O8:P9"/>
-    <mergeCell ref="R8:S9"/>
-    <mergeCell ref="D1:Q1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:L2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mazenelnahla/Desktop/Projects/React Projects/degree/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4457450D-E00B-204B-9A39-00B356085183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA202E-E100-C04F-ADCC-86BF79C81BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="2080" windowWidth="27640" windowHeight="16680" xr2:uid="{685E02A3-3CA7-7740-8516-46D23A04F233}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="33600" windowHeight="18860" xr2:uid="{685E02A3-3CA7-7740-8516-46D23A04F233}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1044,7 +1044,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>503952</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>290861</xdr:rowOff>
+      <xdr:rowOff>214661</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1058,9 +1058,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11026359948" y="3180177"/>
-          <a:ext cx="0" cy="285684"/>
+        <a:xfrm flipH="1">
+          <a:off x="2152724" y="2277809"/>
+          <a:ext cx="0" cy="209484"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1107,9 +1107,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11022293169" y="3196405"/>
-          <a:ext cx="1" cy="270696"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7127218" y="2294037"/>
+          <a:ext cx="1" cy="201403"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1141,8 +1141,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>520065</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>290511</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1085</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1156,9 +1156,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11024324535" y="8434705"/>
-          <a:ext cx="0" cy="288606"/>
+        <a:xfrm>
+          <a:off x="4641995" y="6062256"/>
+          <a:ext cx="0" cy="199706"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1205,9 +1205,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="11018274890" y="4635500"/>
-          <a:ext cx="8075488" cy="11043"/>
+        <a:xfrm flipV="1">
+          <a:off x="2162294" y="3319825"/>
+          <a:ext cx="9890920" cy="11043"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1238,7 +1238,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>541482</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>291581</xdr:rowOff>
+      <xdr:rowOff>215381</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1252,9 +1252,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11024303118" y="3189721"/>
-          <a:ext cx="0" cy="276860"/>
+        <a:xfrm flipH="1">
+          <a:off x="4663412" y="2287353"/>
+          <a:ext cx="0" cy="200660"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1301,9 +1301,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11026387649" y="9601200"/>
-          <a:ext cx="0" cy="606352"/>
+        <a:xfrm>
+          <a:off x="2125023" y="6907018"/>
+          <a:ext cx="0" cy="445485"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1350,9 +1350,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11026308153" y="11232198"/>
-          <a:ext cx="2344" cy="169159"/>
+        <a:xfrm>
+          <a:off x="2202175" y="8124709"/>
+          <a:ext cx="2344" cy="99866"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1398,9 +1398,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11020126255" y="11070570"/>
-          <a:ext cx="0" cy="283244"/>
+        <a:xfrm>
+          <a:off x="9899277" y="7963081"/>
+          <a:ext cx="0" cy="213951"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1447,9 +1447,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11025327200" y="12535830"/>
-          <a:ext cx="998241" cy="1610"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2187231" y="9015034"/>
+          <a:ext cx="1300813" cy="1610"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1494,9 +1494,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11026322333" y="12538321"/>
-          <a:ext cx="191" cy="301401"/>
+        <a:xfrm flipH="1">
+          <a:off x="2190148" y="9017525"/>
+          <a:ext cx="191" cy="232108"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1542,9 +1542,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13522462764" y="7929000"/>
-          <a:ext cx="999015" cy="0"/>
+        <a:xfrm flipH="1">
+          <a:off x="4955891" y="8024300"/>
+          <a:ext cx="997691" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1575,7 +1575,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>9461</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>291371</xdr:rowOff>
+      <xdr:rowOff>215171</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1589,9 +1589,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11024162039" y="13845674"/>
-          <a:ext cx="626" cy="136297"/>
+        <a:xfrm>
+          <a:off x="4955151" y="10003144"/>
+          <a:ext cx="626" cy="60097"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1637,9 +1637,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="13510652686" y="7962512"/>
-          <a:ext cx="1390408" cy="0"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7064988" y="8102994"/>
+          <a:ext cx="1388898" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1684,9 +1684,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11022349824" y="11281192"/>
-          <a:ext cx="0" cy="78025"/>
+        <a:xfrm>
+          <a:off x="7070564" y="8173703"/>
+          <a:ext cx="0" cy="8732"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1732,9 +1732,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13521494367" y="8025076"/>
-          <a:ext cx="4722802" cy="13287"/>
+        <a:xfrm flipH="1">
+          <a:off x="2205795" y="8120376"/>
+          <a:ext cx="4714860" cy="13287"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1779,8 +1779,8 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11022498625" y="11076940"/>
+        <a:xfrm flipH="1">
+          <a:off x="6915128" y="7969451"/>
           <a:ext cx="6635" cy="160020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1827,9 +1827,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="11022316438" y="9700092"/>
-          <a:ext cx="1006702" cy="168"/>
+        <a:xfrm flipV="1">
+          <a:off x="5945962" y="7005910"/>
+          <a:ext cx="1157988" cy="168"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1874,9 +1874,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13535528968" y="6892913"/>
-          <a:ext cx="23667" cy="2857193"/>
+        <a:xfrm>
+          <a:off x="5938543" y="7016518"/>
+          <a:ext cx="23667" cy="2895388"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1922,8 +1922,8 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11022314760" y="9612035"/>
+        <a:xfrm>
+          <a:off x="7102027" y="6917853"/>
           <a:ext cx="3601" cy="88225"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1956,7 +1956,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>555207</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>289490</xdr:rowOff>
+      <xdr:rowOff>213290</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1970,9 +1970,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11024289393" y="5819069"/>
-          <a:ext cx="0" cy="274321"/>
+        <a:xfrm flipH="1">
+          <a:off x="4677137" y="4181660"/>
+          <a:ext cx="0" cy="198121"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2005,7 +2005,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>570447</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>289490</xdr:rowOff>
+      <xdr:rowOff>213290</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2019,9 +2019,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11022254853" y="5819069"/>
-          <a:ext cx="0" cy="274321"/>
+        <a:xfrm flipH="1">
+          <a:off x="7165535" y="4181660"/>
+          <a:ext cx="0" cy="198121"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2068,9 +2068,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11020126789" y="5811449"/>
-          <a:ext cx="0" cy="286044"/>
+        <a:xfrm flipH="1">
+          <a:off x="9898743" y="4174040"/>
+          <a:ext cx="0" cy="216751"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2097,7 +2097,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>8434</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>288925</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
@@ -2117,9 +2117,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11020124466" y="6969125"/>
-          <a:ext cx="0" cy="611186"/>
+        <a:xfrm>
+          <a:off x="9901066" y="5012657"/>
+          <a:ext cx="0" cy="447645"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2166,9 +2166,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11022304334" y="6979920"/>
-          <a:ext cx="0" cy="301387"/>
+        <a:xfrm>
+          <a:off x="7116054" y="5020778"/>
+          <a:ext cx="0" cy="209813"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2214,9 +2214,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11022298700" y="7278912"/>
-          <a:ext cx="978720" cy="2204"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5991682" y="5228196"/>
+          <a:ext cx="1130006" cy="2204"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2261,9 +2261,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13514192903" y="5190355"/>
-          <a:ext cx="4300" cy="937249"/>
+        <a:xfrm>
+          <a:off x="5994651" y="5230398"/>
+          <a:ext cx="4300" cy="941151"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2308,9 +2308,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="13514181198" y="6086636"/>
-          <a:ext cx="3903641" cy="29263"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2111122" y="6130581"/>
+          <a:ext cx="3899534" cy="29263"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2334,14 +2334,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>469005</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>7754</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>469005</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>959</xdr:rowOff>
+      <xdr:rowOff>7754</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2355,9 +2355,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11026394895" y="8653780"/>
-          <a:ext cx="0" cy="72079"/>
+        <a:xfrm>
+          <a:off x="2117777" y="6268631"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2403,9 +2403,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11022314760" y="8461375"/>
-          <a:ext cx="0" cy="287336"/>
+        <a:xfrm>
+          <a:off x="7105628" y="6088926"/>
+          <a:ext cx="0" cy="195762"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2437,8 +2437,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>4890</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>215027</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1801</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2452,9 +2452,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11020128010" y="8463280"/>
-          <a:ext cx="0" cy="184547"/>
+        <a:xfrm>
+          <a:off x="9897522" y="6090831"/>
+          <a:ext cx="0" cy="171847"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2479,14 +2479,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>8434</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>5214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>464820</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>212632</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>5214</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2500,9 +2500,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11018321880" y="8638540"/>
-          <a:ext cx="1802586" cy="6892"/>
+        <a:xfrm flipH="1">
+          <a:off x="9901066" y="6266091"/>
+          <a:ext cx="2105158" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2526,8 +2526,8 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>5214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
@@ -2547,9 +2547,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11018306640" y="8638540"/>
-          <a:ext cx="0" cy="96135"/>
+        <a:xfrm>
+          <a:off x="12021464" y="6266091"/>
+          <a:ext cx="0" cy="4561"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2595,9 +2595,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11020125470" y="9616440"/>
-          <a:ext cx="0" cy="301387"/>
+        <a:xfrm>
+          <a:off x="9900062" y="6922258"/>
+          <a:ext cx="0" cy="209813"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2643,9 +2643,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11020127006" y="9923780"/>
-          <a:ext cx="4044494" cy="7620"/>
+        <a:xfrm flipH="1">
+          <a:off x="4946316" y="7138024"/>
+          <a:ext cx="4952210" cy="7620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2690,9 +2690,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13532193572" y="7100924"/>
-          <a:ext cx="10624" cy="953046"/>
+        <a:xfrm flipH="1">
+          <a:off x="8451272" y="7150076"/>
+          <a:ext cx="10624" cy="957301"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2737,9 +2737,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11020123646" y="7078980"/>
-          <a:ext cx="2020120" cy="9096"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7427908" y="5119838"/>
+          <a:ext cx="2473978" cy="9096"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2784,9 +2784,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11022143766" y="7078980"/>
-          <a:ext cx="0" cy="479675"/>
+        <a:xfrm>
+          <a:off x="7427908" y="5119838"/>
+          <a:ext cx="0" cy="318808"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2832,9 +2832,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11018258114" y="6972300"/>
-          <a:ext cx="2806" cy="375920"/>
+        <a:xfrm flipH="1">
+          <a:off x="12067184" y="5013158"/>
+          <a:ext cx="2806" cy="284346"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2880,9 +2880,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11018252480" y="7340600"/>
-          <a:ext cx="3709220" cy="1476"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7609974" y="5289884"/>
+          <a:ext cx="4465650" cy="1476"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2927,9 +2927,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11021946460" y="7348220"/>
-          <a:ext cx="7620" cy="215900"/>
+        <a:xfrm>
+          <a:off x="7617594" y="5297504"/>
+          <a:ext cx="7620" cy="146607"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2975,9 +2975,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11024311200" y="9625965"/>
-          <a:ext cx="5715" cy="578485"/>
+        <a:xfrm>
+          <a:off x="4649615" y="6931783"/>
+          <a:ext cx="5715" cy="417618"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3024,8 +3024,8 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13523463734" y="7077395"/>
+        <a:xfrm>
+          <a:off x="4953936" y="7164312"/>
           <a:ext cx="0" cy="159149"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3072,9 +3072,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11020117660" y="10022840"/>
-          <a:ext cx="6266180" cy="7620"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2128832" y="7237084"/>
+          <a:ext cx="7779040" cy="7620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3119,9 +3119,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11020110040" y="10038080"/>
-          <a:ext cx="7620" cy="179955"/>
+        <a:xfrm flipH="1">
+          <a:off x="9907872" y="7252324"/>
+          <a:ext cx="7620" cy="110662"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3167,9 +3167,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11024162392" y="11283135"/>
-          <a:ext cx="0" cy="78025"/>
+        <a:xfrm>
+          <a:off x="4955424" y="8175646"/>
+          <a:ext cx="0" cy="8732"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3194,8 +3194,8 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>270809</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>6783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
@@ -3215,9 +3215,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11025312259" y="9872009"/>
-          <a:ext cx="7321" cy="2665431"/>
+        <a:xfrm flipH="1">
+          <a:off x="3495664" y="7114327"/>
+          <a:ext cx="7321" cy="1902317"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3241,14 +3241,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>196103</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>280147</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3421</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>525780</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>3421</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3262,9 +3262,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11024318820" y="9881347"/>
-          <a:ext cx="1002777" cy="11953"/>
+        <a:xfrm>
+          <a:off x="3493647" y="7110965"/>
+          <a:ext cx="1154063" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3309,9 +3309,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13535532328" y="9746744"/>
-          <a:ext cx="1008762" cy="276"/>
+        <a:xfrm flipH="1">
+          <a:off x="4952210" y="9908544"/>
+          <a:ext cx="1006640" cy="276"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3356,9 +3356,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11026355900" y="4362450"/>
-          <a:ext cx="0" cy="566421"/>
+        <a:xfrm flipH="1">
+          <a:off x="2156772" y="3138348"/>
+          <a:ext cx="0" cy="405555"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3385,7 +3385,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>508000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
@@ -3405,9 +3405,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11018272350" y="4629150"/>
-          <a:ext cx="6350" cy="314575"/>
+        <a:xfrm>
+          <a:off x="12049404" y="3316148"/>
+          <a:ext cx="6350" cy="242609"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3453,9 +3453,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11026670640" y="4359966"/>
-          <a:ext cx="0" cy="301387"/>
+        <a:xfrm>
+          <a:off x="1842032" y="3135864"/>
+          <a:ext cx="0" cy="209814"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3501,9 +3501,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11026668715" y="4659790"/>
-          <a:ext cx="713676" cy="3318"/>
+        <a:xfrm flipH="1">
+          <a:off x="978995" y="3344115"/>
+          <a:ext cx="864962" cy="3318"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3548,9 +3548,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11027376869" y="4657586"/>
-          <a:ext cx="5521" cy="1278835"/>
+        <a:xfrm>
+          <a:off x="977570" y="3303766"/>
+          <a:ext cx="5521" cy="943555"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3595,9 +3595,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="11026333813" y="5928697"/>
-          <a:ext cx="1037535" cy="2203"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="990038" y="4291288"/>
+          <a:ext cx="1188821" cy="2203"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3642,9 +3642,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="11026333813" y="5925379"/>
-          <a:ext cx="0" cy="171010"/>
+        <a:xfrm>
+          <a:off x="2178859" y="4287970"/>
+          <a:ext cx="0" cy="101717"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3690,9 +3690,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13523458779" y="7925973"/>
-          <a:ext cx="0" cy="159149"/>
+        <a:xfrm>
+          <a:off x="4958891" y="8021273"/>
+          <a:ext cx="0" cy="164002"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3738,8 +3738,8 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13536540753" y="9743115"/>
+        <a:xfrm>
+          <a:off x="4952547" y="9904915"/>
           <a:ext cx="0" cy="156221"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3786,9 +3786,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="13518096544" y="6074932"/>
-          <a:ext cx="0" cy="157739"/>
+        <a:xfrm>
+          <a:off x="2099417" y="6118877"/>
+          <a:ext cx="0" cy="153427"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
